--- a/education_surveys/036_institutional_digital_ethics_awareness_survey--education_surveys.xlsx
+++ b/education_surveys/036_institutional_digital_ethics_awareness_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey</t>
+          <t>has_digital_ethics_training</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Institutional Digital Ethics Awareness</t>
+          <t>Is digital ethics training available within the institution?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_category</t>
+          <t>digital_ethics_training_frequency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Education Surveys</t>
+          <t>How often is digital ethics training provided to employees within the institution?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>digital_ethics_training_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How many hours of digital ethics training are provided to employees within the institution?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>top_priority_areas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Which of the following areas of digital ethics should be the top priority for the institution?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>primary_digital_ethics_goal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What is the primary goal of digital ethics training within the institution?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>digital_ethics_policy_communication</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How does the institution communicate digital ethics policies to employees?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>digital_ethics_policies_implementation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What is the main method used by the institution to ensure digital ethics practices are being followed?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>digital_ethics_policies_revision</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How often are digital ethics policies reviewed within the institution?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>departmental_digital_ethics_policies</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Are there any digital ethics policies that are specific to a certain department within the institution?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>responsible_person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Who is responsible for implementing and enforcing digital ethics policies within the institution?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_description</t>
+          <t>has_digital_ethics_incidents</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Are there any digital ethics related incidents that have occurred within the institution?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_output_file</t>
+          <t>output_file</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_assigned_tool</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_form_id</t>
+          <t>form_id</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_form_category</t>
+          <t>form_category</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -868,12 +868,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,100 +896,695 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_category_choices</t>
+          <t>digital_ethics_training_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_survey_category_choices</t>
+          <t>digital_ethics_training_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_output_file_choices</t>
+          <t>digital_ethics_training_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>education_surveys</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Education Surveys</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_output_file_choices</t>
+          <t>digital_ethics_training_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_assigned_tool_choices</t>
+          <t>digital_ethics_training_frequency_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>institutional_digital_ethics_awareness_survey_assigned_tool_choices</t>
+          <t>top_priority_areas_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>digital_security</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>Digital Security</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>top_priority_areas_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>data_protection</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Data Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>top_priority_areas_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>user_authentication</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>User Authentication</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>top_priority_areas_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>digital_signature</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Digital Signature</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>top_priority_areas_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>data_breach</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Data Breach</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>top_priority_areas_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>compliance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>primary_digital_ethics_goal_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>to_increase_user_engagement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>To increase user engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>primary_digital_ethics_goal_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>to_increase_productivity</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>To increase productivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>primary_digital_ethics_goal_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>to_improve_security</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>To improve security</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>primary_digital_ethics_goal_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>to_reduce_costs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>To reduce costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>primary_digital_ethics_goal_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>to_enhance_customer_satisfaction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>To enhance customer satisfaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>primary_digital_ethics_goal_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>digital_ethics_policy_communication_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>digital_ethics_policy_communication_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Newsletter</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>digital_ethics_policy_communication_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>social_media</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Social Media</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>digital_ethics_policy_communication_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>training_sessions</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Training sessions</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>digital_ethics_policy_communication_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_implementation_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>audits</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_implementation_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>monitoring</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_implementation_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>regular_checklists</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Regular checklists</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_implementation_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_revision_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>annually</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_revision_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_revision_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_revision_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>digital_ethics_policies_revision_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>departmental_digital_ethics_policies_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>departmental_digital_ethics_policies_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>responsible_person_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>management</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>responsible_person_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>employees</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>responsible_person_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>it_department</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>IT Department</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>responsible_person_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>other_(please_specify)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Other (please specify)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>output_file_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>education_surveys</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Education Surveys</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>output_file_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>assigned_tool_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>assigned_tool_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
